--- a/Project/웹페이지개발.xlsx
+++ b/Project/웹페이지개발.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\MBCA\Web\Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15ECD080-895D-4CFD-BDE6-BA51373AD02F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA58BE0A-8536-4131-A63C-673AF49C7193}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-16200" windowWidth="14610" windowHeight="15405" activeTab="7" xr2:uid="{E10337B3-68D7-437E-9940-2D2327D790D9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="8" xr2:uid="{E10337B3-68D7-437E-9940-2D2327D790D9}"/>
   </bookViews>
   <sheets>
     <sheet name="서론" sheetId="4" r:id="rId1"/>
@@ -21,6 +21,7 @@
     <sheet name="food.html 레이아웃" sheetId="6" r:id="rId6"/>
     <sheet name="registration.html 레이아웃" sheetId="7" r:id="rId7"/>
     <sheet name="login.html 레이아웃" sheetId="8" r:id="rId8"/>
+    <sheet name="board.html 레이아웃)" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="141">
   <si>
     <t>주제 선정</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -563,13 +564,27 @@
   <si>
     <t>span</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>login</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>대문자 , 소문자 구별하기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>board_item</t>
+  </si>
+  <si>
+    <t>record_line</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -620,6 +635,12 @@
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="13">
@@ -970,7 +991,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -5238,11 +5259,6 @@
       <c r="J15" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="K15" s="41"/>
-      <c r="L15" s="41"/>
-      <c r="M15" s="41"/>
-      <c r="N15" s="41"/>
-      <c r="O15" s="41"/>
       <c r="Q15" s="5"/>
       <c r="S15" s="4"/>
       <c r="T15" s="5"/>
@@ -5257,11 +5273,6 @@
       </c>
       <c r="F16" s="5"/>
       <c r="I16" s="4"/>
-      <c r="K16" s="41"/>
-      <c r="L16" s="41"/>
-      <c r="M16" s="41"/>
-      <c r="N16" s="41"/>
-      <c r="O16" s="41"/>
       <c r="Q16" s="5"/>
       <c r="S16" s="27" t="s">
         <v>98</v>
@@ -5310,9 +5321,6 @@
       <c r="L18" s="27" t="s">
         <v>126</v>
       </c>
-      <c r="M18" s="41"/>
-      <c r="N18" s="41"/>
-      <c r="O18" s="41"/>
       <c r="P18" s="5"/>
       <c r="Q18" s="5"/>
       <c r="S18" s="4"/>
@@ -5336,11 +5344,6 @@
       <c r="F19" s="5"/>
       <c r="I19" s="4"/>
       <c r="J19" s="4"/>
-      <c r="K19" s="41"/>
-      <c r="L19" s="41"/>
-      <c r="M19" s="41"/>
-      <c r="N19" s="41"/>
-      <c r="O19" s="41"/>
       <c r="P19" s="5"/>
       <c r="Q19" s="5"/>
       <c r="S19" s="4"/>
@@ -5364,12 +5367,9 @@
       <c r="F20" s="5"/>
       <c r="I20" s="4"/>
       <c r="J20" s="4"/>
-      <c r="L20" s="41" t="s">
+      <c r="L20" t="s">
         <v>121</v>
       </c>
-      <c r="M20" s="41"/>
-      <c r="N20" s="41"/>
-      <c r="O20" s="41"/>
       <c r="P20" s="5"/>
       <c r="Q20" s="5"/>
       <c r="S20" s="4"/>
@@ -5393,10 +5393,6 @@
       <c r="F21" s="5"/>
       <c r="I21" s="4"/>
       <c r="J21" s="4"/>
-      <c r="L21" s="41"/>
-      <c r="M21" s="41"/>
-      <c r="N21" s="41"/>
-      <c r="O21" s="41"/>
       <c r="P21" s="5"/>
       <c r="Q21" s="5"/>
       <c r="S21" s="4"/>
@@ -5420,11 +5416,9 @@
       <c r="F22" s="5"/>
       <c r="I22" s="4"/>
       <c r="J22" s="4"/>
-      <c r="M22" s="41" t="s">
+      <c r="M22" t="s">
         <v>122</v>
       </c>
-      <c r="N22" s="41"/>
-      <c r="O22" s="41"/>
       <c r="P22" s="5"/>
       <c r="Q22" s="5"/>
       <c r="S22" s="4"/>
@@ -5448,11 +5442,9 @@
       <c r="F23" s="5"/>
       <c r="I23" s="4"/>
       <c r="J23" s="4"/>
-      <c r="M23" s="41" t="s">
+      <c r="M23" t="s">
         <v>123</v>
       </c>
-      <c r="N23" s="41"/>
-      <c r="O23" s="41"/>
       <c r="P23" s="5"/>
       <c r="Q23" s="5"/>
       <c r="S23" s="4"/>
@@ -5467,10 +5459,9 @@
       <c r="F24" s="5"/>
       <c r="I24" s="4"/>
       <c r="J24" s="4"/>
-      <c r="M24" s="42" t="s">
+      <c r="M24" t="s">
         <v>86</v>
       </c>
-      <c r="O24" s="41"/>
       <c r="P24" s="5"/>
       <c r="Q24" s="5"/>
       <c r="S24" s="4"/>
@@ -5485,13 +5476,12 @@
       <c r="F25" s="5"/>
       <c r="I25" s="4"/>
       <c r="J25" s="4"/>
-      <c r="M25" s="42" t="s">
+      <c r="M25" t="s">
         <v>124</v>
       </c>
-      <c r="N25" s="41" t="s">
+      <c r="N25" t="s">
         <v>125</v>
       </c>
-      <c r="O25" s="41"/>
       <c r="P25" s="5"/>
       <c r="Q25" s="5"/>
       <c r="S25" s="4"/>
@@ -5506,11 +5496,9 @@
       <c r="F26" s="5"/>
       <c r="I26" s="4"/>
       <c r="J26" s="4"/>
-      <c r="M26" s="41"/>
-      <c r="N26" s="41" t="s">
+      <c r="N26" t="s">
         <v>125</v>
       </c>
-      <c r="O26" s="41"/>
       <c r="P26" s="5"/>
       <c r="Q26" s="5"/>
       <c r="S26" s="4"/>
@@ -5525,11 +5513,9 @@
       <c r="F27" s="5"/>
       <c r="I27" s="4"/>
       <c r="J27" s="4"/>
-      <c r="M27" s="41"/>
-      <c r="N27" s="41" t="s">
+      <c r="N27" t="s">
         <v>125</v>
       </c>
-      <c r="O27" s="41"/>
       <c r="P27" s="5"/>
       <c r="Q27" s="5"/>
       <c r="S27" s="4"/>
@@ -5544,11 +5530,9 @@
       <c r="F28" s="5"/>
       <c r="I28" s="4"/>
       <c r="J28" s="4"/>
-      <c r="M28" s="41"/>
-      <c r="N28" s="41" t="s">
+      <c r="N28" t="s">
         <v>125</v>
       </c>
-      <c r="O28" s="41"/>
       <c r="P28" s="5"/>
       <c r="Q28" s="5"/>
       <c r="S28" s="4"/>
@@ -5563,11 +5547,9 @@
       <c r="F29" s="5"/>
       <c r="I29" s="4"/>
       <c r="J29" s="4"/>
-      <c r="M29" s="41"/>
-      <c r="N29" s="41" t="s">
+      <c r="N29" t="s">
         <v>125</v>
       </c>
-      <c r="O29" s="41"/>
       <c r="P29" s="5"/>
       <c r="Q29" s="5"/>
       <c r="S29" s="4"/>
@@ -5582,11 +5564,9 @@
       <c r="F30" s="5"/>
       <c r="I30" s="4"/>
       <c r="J30" s="4"/>
-      <c r="M30" s="41"/>
-      <c r="N30" s="41" t="s">
+      <c r="N30" t="s">
         <v>125</v>
       </c>
-      <c r="O30" s="41"/>
       <c r="P30" s="5"/>
       <c r="Q30" s="5"/>
       <c r="S30" s="4"/>
@@ -5601,11 +5581,9 @@
       <c r="F31" s="5"/>
       <c r="I31" s="4"/>
       <c r="J31" s="4"/>
-      <c r="M31" s="41"/>
-      <c r="N31" s="41" t="s">
+      <c r="N31" t="s">
         <v>125</v>
       </c>
-      <c r="O31" s="41"/>
       <c r="P31" s="5"/>
       <c r="Q31" s="5"/>
       <c r="S31" s="4"/>
@@ -5620,11 +5598,9 @@
       <c r="F32" s="5"/>
       <c r="I32" s="4"/>
       <c r="J32" s="4"/>
-      <c r="M32" s="41"/>
-      <c r="N32" s="41" t="s">
+      <c r="N32" t="s">
         <v>125</v>
       </c>
-      <c r="O32" s="41"/>
       <c r="P32" s="5"/>
       <c r="Q32" s="5"/>
       <c r="S32" s="4"/>
@@ -5639,11 +5615,9 @@
       <c r="F33" s="5"/>
       <c r="I33" s="4"/>
       <c r="J33" s="4"/>
-      <c r="M33" s="41"/>
-      <c r="N33" s="42" t="s">
+      <c r="N33" t="s">
         <v>125</v>
       </c>
-      <c r="O33" s="41"/>
       <c r="P33" s="5"/>
       <c r="Q33" s="5"/>
       <c r="S33" s="4"/>
@@ -5657,15 +5631,12 @@
       <c r="F34" s="5"/>
       <c r="I34" s="4"/>
       <c r="J34" s="4"/>
-      <c r="K34" s="41" t="s">
+      <c r="K34" t="s">
         <v>86</v>
       </c>
       <c r="L34" s="27" t="s">
         <v>127</v>
       </c>
-      <c r="M34" s="41"/>
-      <c r="N34" s="41"/>
-      <c r="O34" s="41"/>
       <c r="P34" s="5"/>
       <c r="Q34" s="5"/>
       <c r="T34" s="5"/>
@@ -5679,12 +5650,9 @@
       <c r="F35" s="5"/>
       <c r="I35" s="4"/>
       <c r="J35" s="4"/>
-      <c r="L35" s="42" t="s">
+      <c r="L35" t="s">
         <v>125</v>
       </c>
-      <c r="M35" s="41"/>
-      <c r="N35" s="41"/>
-      <c r="O35" s="41"/>
       <c r="P35" s="5"/>
       <c r="Q35" s="5"/>
       <c r="S35" s="4"/>
@@ -5699,13 +5667,9 @@
       <c r="F36" s="5"/>
       <c r="I36" s="4"/>
       <c r="J36" s="4"/>
-      <c r="K36" s="41"/>
-      <c r="L36" s="42" t="s">
+      <c r="L36" t="s">
         <v>125</v>
       </c>
-      <c r="M36" s="41"/>
-      <c r="N36" s="41"/>
-      <c r="O36" s="41"/>
       <c r="P36" s="5"/>
       <c r="Q36" s="5"/>
       <c r="S36" s="4"/>
@@ -5738,12 +5702,6 @@
       <c r="E38" s="4"/>
       <c r="F38" s="5"/>
       <c r="I38" s="4"/>
-      <c r="J38" s="41"/>
-      <c r="K38" s="41"/>
-      <c r="L38" s="41"/>
-      <c r="M38" s="41"/>
-      <c r="N38" s="41"/>
-      <c r="O38" s="41"/>
       <c r="Q38" s="5"/>
       <c r="S38" s="4"/>
       <c r="T38" s="5"/>
@@ -5756,12 +5714,6 @@
       <c r="E39" s="4"/>
       <c r="F39" s="5"/>
       <c r="I39" s="4"/>
-      <c r="J39" s="41"/>
-      <c r="K39" s="41"/>
-      <c r="L39" s="41"/>
-      <c r="M39" s="41"/>
-      <c r="N39" s="41"/>
-      <c r="O39" s="41"/>
       <c r="Q39" s="5"/>
       <c r="S39" s="4"/>
       <c r="T39" s="5"/>
@@ -5774,12 +5726,6 @@
       <c r="E40" s="4"/>
       <c r="F40" s="5"/>
       <c r="I40" s="4"/>
-      <c r="J40" s="41"/>
-      <c r="K40" s="41"/>
-      <c r="L40" s="41"/>
-      <c r="M40" s="41"/>
-      <c r="N40" s="41"/>
-      <c r="O40" s="41"/>
       <c r="Q40" s="5"/>
       <c r="S40" s="4"/>
       <c r="T40" s="5"/>
@@ -5958,13 +5904,13 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFBC5185-E3BA-4BBD-AD16-13912DAD2841}">
-  <dimension ref="A1:S44"/>
+  <dimension ref="A1:V44"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="9" style="29"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="29" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" s="29" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="29" t="s">
         <v>93</v>
       </c>
@@ -5972,8 +5918,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="1:19" s="29" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="1:22" s="29" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="29">
         <v>0</v>
       </c>
@@ -5999,8 +5945,11 @@
       <c r="Q3" s="33"/>
       <c r="R3" s="33"/>
       <c r="S3" s="34"/>
-    </row>
-    <row r="4" spans="1:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="U3" s="29" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="31">
         <v>0</v>
       </c>
@@ -6008,8 +5957,11 @@
         <v>99</v>
       </c>
       <c r="S4" s="5"/>
-    </row>
-    <row r="5" spans="1:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="V4" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="31"/>
       <c r="D5" s="1" t="s">
         <v>87</v>
@@ -6031,7 +5983,7 @@
       <c r="Q5" s="3"/>
       <c r="S5" s="5"/>
     </row>
-    <row r="6" spans="1:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="31"/>
       <c r="D6" s="4"/>
       <c r="H6" s="24" t="s">
@@ -6049,7 +6001,7 @@
       <c r="Q6" s="5"/>
       <c r="S6" s="5"/>
     </row>
-    <row r="7" spans="1:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="31"/>
       <c r="D7" s="4"/>
       <c r="E7" s="36">
@@ -6058,7 +6010,7 @@
       <c r="Q7" s="5"/>
       <c r="S7" s="5"/>
     </row>
-    <row r="8" spans="1:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B8" s="31"/>
       <c r="D8" s="4"/>
       <c r="E8" s="24" t="s">
@@ -6079,13 +6031,13 @@
       <c r="Q8" s="5"/>
       <c r="S8" s="5"/>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B9" s="31"/>
       <c r="D9" s="4"/>
       <c r="Q9" s="5"/>
       <c r="S9" s="5"/>
     </row>
-    <row r="10" spans="1:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" s="31"/>
       <c r="D10" s="6"/>
       <c r="E10" s="7"/>
@@ -6103,11 +6055,11 @@
       <c r="Q10" s="8"/>
       <c r="S10" s="5"/>
     </row>
-    <row r="11" spans="1:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="31"/>
       <c r="S11" s="5"/>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B12" s="31"/>
       <c r="D12" s="1" t="s">
         <v>88</v>
@@ -6127,19 +6079,19 @@
       <c r="Q12" s="3"/>
       <c r="S12" s="5"/>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B13" s="31"/>
       <c r="D13" s="4"/>
       <c r="Q13" s="5"/>
       <c r="S13" s="5"/>
     </row>
-    <row r="14" spans="1:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" s="31"/>
       <c r="D14" s="4"/>
       <c r="Q14" s="5"/>
       <c r="S14" s="5"/>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B15" s="31"/>
       <c r="D15" s="4"/>
       <c r="E15" s="1" t="s">
@@ -6161,19 +6113,18 @@
       <c r="Q15" s="5"/>
       <c r="S15" s="5"/>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B16" s="31"/>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
       <c r="F16" s="5"/>
       <c r="H16" s="4"/>
-      <c r="I16" s="41" t="s">
+      <c r="I16" t="s">
         <v>90</v>
       </c>
       <c r="J16" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="K16" s="41"/>
       <c r="M16" s="5"/>
       <c r="O16" s="4"/>
       <c r="P16" s="5"/>
@@ -6186,9 +6137,6 @@
       <c r="E17" s="4"/>
       <c r="F17" s="5"/>
       <c r="H17" s="4"/>
-      <c r="I17" s="41"/>
-      <c r="J17" s="41"/>
-      <c r="K17" s="41"/>
       <c r="M17" s="5"/>
       <c r="O17" s="4"/>
       <c r="P17" s="5"/>
@@ -6201,12 +6149,9 @@
       <c r="E18" s="4"/>
       <c r="F18" s="5"/>
       <c r="H18" s="4"/>
-      <c r="I18" s="41"/>
-      <c r="J18" s="41" t="s">
+      <c r="J18" t="s">
         <v>86</v>
       </c>
-      <c r="K18" s="41"/>
-      <c r="L18" s="41"/>
       <c r="M18" s="5"/>
       <c r="O18" s="4"/>
       <c r="P18" s="5"/>
@@ -6219,11 +6164,10 @@
       <c r="E19" s="4"/>
       <c r="F19" s="5"/>
       <c r="H19" s="4"/>
-      <c r="J19" s="41"/>
-      <c r="K19" s="41" t="s">
+      <c r="K19" t="s">
         <v>136</v>
       </c>
-      <c r="L19" s="41" t="s">
+      <c r="L19" t="s">
         <v>123</v>
       </c>
       <c r="M19" s="5"/>
@@ -6238,11 +6182,10 @@
       <c r="E20" s="4"/>
       <c r="F20" s="5"/>
       <c r="H20" s="4"/>
-      <c r="J20" s="41"/>
-      <c r="K20" s="41" t="s">
+      <c r="K20" t="s">
         <v>124</v>
       </c>
-      <c r="L20" s="41" t="s">
+      <c r="L20" t="s">
         <v>125</v>
       </c>
       <c r="M20" s="5"/>
@@ -6269,9 +6212,6 @@
       <c r="E22" s="4"/>
       <c r="F22" s="5"/>
       <c r="H22" s="4"/>
-      <c r="I22" s="41"/>
-      <c r="J22" s="41"/>
-      <c r="K22" s="41"/>
       <c r="M22" s="5"/>
       <c r="O22" s="4"/>
       <c r="P22" s="5"/>
@@ -6284,9 +6224,6 @@
       <c r="E23" s="4"/>
       <c r="F23" s="5"/>
       <c r="H23" s="4"/>
-      <c r="I23" s="41"/>
-      <c r="J23" s="41"/>
-      <c r="K23" s="41"/>
       <c r="M23" s="5"/>
       <c r="O23" s="4"/>
       <c r="P23" s="5"/>
@@ -6301,9 +6238,6 @@
       </c>
       <c r="F24" s="5"/>
       <c r="H24" s="4"/>
-      <c r="I24" s="41"/>
-      <c r="J24" s="41"/>
-      <c r="K24" s="41"/>
       <c r="M24" s="5"/>
       <c r="O24" s="27" t="s">
         <v>98</v>
@@ -6318,9 +6252,6 @@
       <c r="E25" s="4"/>
       <c r="F25" s="5"/>
       <c r="H25" s="4"/>
-      <c r="I25" s="41"/>
-      <c r="J25" s="41"/>
-      <c r="K25" s="41"/>
       <c r="M25" s="5"/>
       <c r="O25" s="4"/>
       <c r="P25" s="5"/>
@@ -6333,9 +6264,6 @@
       <c r="E26" s="4"/>
       <c r="F26" s="5"/>
       <c r="H26" s="4"/>
-      <c r="I26" s="41"/>
-      <c r="J26" s="41"/>
-      <c r="K26" s="41"/>
       <c r="M26" s="5"/>
       <c r="O26" s="4"/>
       <c r="P26" s="5"/>
@@ -6348,9 +6276,6 @@
       <c r="E27" s="4"/>
       <c r="F27" s="5"/>
       <c r="H27" s="4"/>
-      <c r="I27" s="41"/>
-      <c r="J27" s="41"/>
-      <c r="K27" s="41"/>
       <c r="M27" s="5"/>
       <c r="O27" s="4"/>
       <c r="P27" s="5"/>
@@ -6363,9 +6288,6 @@
       <c r="E28" s="4"/>
       <c r="F28" s="5"/>
       <c r="H28" s="4"/>
-      <c r="I28" s="41"/>
-      <c r="J28" s="41"/>
-      <c r="K28" s="41"/>
       <c r="M28" s="5"/>
       <c r="O28" s="4"/>
       <c r="P28" s="5"/>
@@ -6378,9 +6300,6 @@
       <c r="E29" s="4"/>
       <c r="F29" s="5"/>
       <c r="H29" s="4"/>
-      <c r="I29" s="41"/>
-      <c r="J29" s="41"/>
-      <c r="K29" s="41"/>
       <c r="M29" s="5"/>
       <c r="O29" s="4"/>
       <c r="P29" s="5"/>
@@ -6533,4 +6452,745 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89FF25E7-13C5-4F01-B428-40BCB1F5A940}">
+  <dimension ref="A1:W45"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="9" style="29"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:23" s="29" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="29" t="s">
+        <v>93</v>
+      </c>
+      <c r="B1" s="29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="1:23" s="29" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="29">
+        <v>0</v>
+      </c>
+      <c r="B3" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="C3" s="33">
+        <v>0</v>
+      </c>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="33"/>
+      <c r="I3" s="33"/>
+      <c r="J3" s="33"/>
+      <c r="K3" s="33"/>
+      <c r="L3" s="33"/>
+      <c r="M3" s="33"/>
+      <c r="N3" s="33"/>
+      <c r="O3" s="33"/>
+      <c r="P3" s="33"/>
+      <c r="Q3" s="33"/>
+      <c r="R3" s="33"/>
+      <c r="S3" s="33"/>
+      <c r="T3" s="33"/>
+      <c r="U3" s="33"/>
+      <c r="V3" s="33"/>
+      <c r="W3" s="34"/>
+    </row>
+    <row r="4" spans="1:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="31">
+        <v>0</v>
+      </c>
+      <c r="D4" t="s">
+        <v>99</v>
+      </c>
+      <c r="W4" s="5"/>
+    </row>
+    <row r="5" spans="1:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="31"/>
+      <c r="D5" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="35">
+        <v>0.5</v>
+      </c>
+      <c r="I5" s="35"/>
+      <c r="J5" s="35"/>
+      <c r="K5" s="35"/>
+      <c r="L5" s="35"/>
+      <c r="M5" s="35"/>
+      <c r="N5" s="35"/>
+      <c r="O5" s="35"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
+      <c r="S5" s="2"/>
+      <c r="T5" s="2"/>
+      <c r="U5" s="3"/>
+      <c r="W5" s="5"/>
+    </row>
+    <row r="6" spans="1:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="31"/>
+      <c r="D6" s="4"/>
+      <c r="H6" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="I6" s="25"/>
+      <c r="J6" s="25"/>
+      <c r="K6" s="25"/>
+      <c r="L6" s="25"/>
+      <c r="M6" s="25"/>
+      <c r="N6" s="25"/>
+      <c r="O6" s="25"/>
+      <c r="P6" s="25"/>
+      <c r="Q6" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="R6" s="25"/>
+      <c r="S6" s="26"/>
+      <c r="U6" s="5"/>
+      <c r="W6" s="5"/>
+    </row>
+    <row r="7" spans="1:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="31"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="36">
+        <v>0.1</v>
+      </c>
+      <c r="U7" s="5"/>
+      <c r="W7" s="5"/>
+    </row>
+    <row r="8" spans="1:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="31"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="F8" s="25"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
+      <c r="K8" s="28"/>
+      <c r="L8" s="28"/>
+      <c r="M8" s="28"/>
+      <c r="N8" s="28"/>
+      <c r="O8" s="28"/>
+      <c r="P8" s="25"/>
+      <c r="Q8" s="25"/>
+      <c r="R8" s="25"/>
+      <c r="S8" s="26"/>
+      <c r="U8" s="5"/>
+      <c r="W8" s="5"/>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="B9" s="31"/>
+      <c r="D9" s="4"/>
+      <c r="U9" s="5"/>
+      <c r="W9" s="5"/>
+    </row>
+    <row r="10" spans="1:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="31"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="7"/>
+      <c r="O10" s="7"/>
+      <c r="P10" s="7"/>
+      <c r="Q10" s="7"/>
+      <c r="R10" s="7"/>
+      <c r="S10" s="7"/>
+      <c r="T10" s="7"/>
+      <c r="U10" s="8"/>
+      <c r="W10" s="5"/>
+    </row>
+    <row r="11" spans="1:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="31"/>
+      <c r="W11" s="5"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="B12" s="31"/>
+      <c r="D12" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="2"/>
+      <c r="S12" s="2"/>
+      <c r="T12" s="2"/>
+      <c r="U12" s="3"/>
+      <c r="W12" s="5"/>
+    </row>
+    <row r="13" spans="1:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="31"/>
+      <c r="D13" s="4"/>
+      <c r="U13" s="5"/>
+      <c r="W13" s="5"/>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="B14" s="31"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F14" s="3"/>
+      <c r="H14" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="3"/>
+      <c r="S14" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="T14" s="3"/>
+      <c r="U14" s="5"/>
+      <c r="W14" s="5"/>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="B15" s="31"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="5"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="J15" s="41"/>
+      <c r="K15" s="41"/>
+      <c r="L15" s="41"/>
+      <c r="M15" s="41"/>
+      <c r="N15" s="41"/>
+      <c r="O15" s="41"/>
+      <c r="Q15" s="5"/>
+      <c r="S15" s="4"/>
+      <c r="T15" s="5"/>
+      <c r="U15" s="5"/>
+      <c r="W15" s="5"/>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="B16" s="31"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="F16" s="5"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="41"/>
+      <c r="J16" s="41"/>
+      <c r="K16" s="41"/>
+      <c r="L16" s="41"/>
+      <c r="M16" s="41"/>
+      <c r="N16" s="41"/>
+      <c r="O16" s="41"/>
+      <c r="Q16" s="5"/>
+      <c r="S16" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="T16" s="5"/>
+      <c r="U16" s="5"/>
+      <c r="W16" s="5"/>
+    </row>
+    <row r="17" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B17" s="31"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="5"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="41"/>
+      <c r="J17" s="41" t="s">
+        <v>86</v>
+      </c>
+      <c r="K17" s="41"/>
+      <c r="L17" s="41"/>
+      <c r="M17" s="41"/>
+      <c r="N17" s="41"/>
+      <c r="O17" s="41"/>
+      <c r="Q17" s="5"/>
+      <c r="S17" s="4"/>
+      <c r="T17" s="5"/>
+      <c r="U17" s="5"/>
+      <c r="W17" s="5"/>
+    </row>
+    <row r="18" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B18" s="31"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="5"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="41"/>
+      <c r="J18" s="41"/>
+      <c r="K18" s="41" t="s">
+        <v>86</v>
+      </c>
+      <c r="L18" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="Q18" s="5"/>
+      <c r="S18" s="4"/>
+      <c r="T18" s="5"/>
+      <c r="U18" s="5"/>
+      <c r="W18" s="5"/>
+    </row>
+    <row r="19" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B19" s="31"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="5"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="41"/>
+      <c r="J19" s="41"/>
+      <c r="K19" s="41"/>
+      <c r="L19" s="41" t="s">
+        <v>136</v>
+      </c>
+      <c r="M19" s="41" t="s">
+        <v>136</v>
+      </c>
+      <c r="N19" s="41" t="s">
+        <v>136</v>
+      </c>
+      <c r="O19" s="41" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q19" s="5"/>
+      <c r="S19" s="4"/>
+      <c r="T19" s="5"/>
+      <c r="U19" s="5"/>
+      <c r="W19" s="5"/>
+    </row>
+    <row r="20" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B20" s="31"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="5"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="41"/>
+      <c r="J20" s="41"/>
+      <c r="K20" s="41"/>
+      <c r="L20" s="41"/>
+      <c r="M20" s="41"/>
+      <c r="N20" s="41"/>
+      <c r="O20" s="41"/>
+      <c r="Q20" s="5"/>
+      <c r="S20" s="4"/>
+      <c r="T20" s="5"/>
+      <c r="U20" s="5"/>
+      <c r="W20" s="5"/>
+    </row>
+    <row r="21" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B21" s="31"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="5"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="41"/>
+      <c r="J21" s="41"/>
+      <c r="K21" s="41" t="s">
+        <v>86</v>
+      </c>
+      <c r="L21" s="42" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q21" s="5"/>
+      <c r="S21" s="4"/>
+      <c r="T21" s="5"/>
+      <c r="U21" s="5"/>
+      <c r="W21" s="5"/>
+    </row>
+    <row r="22" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B22" s="31"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="5"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="41"/>
+      <c r="J22" s="41"/>
+      <c r="K22" s="41"/>
+      <c r="L22" s="41" t="s">
+        <v>136</v>
+      </c>
+      <c r="M22" s="41" t="s">
+        <v>136</v>
+      </c>
+      <c r="N22" s="41" t="s">
+        <v>136</v>
+      </c>
+      <c r="O22" s="41" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q22" s="5"/>
+      <c r="S22" s="4"/>
+      <c r="T22" s="5"/>
+      <c r="U22" s="5"/>
+      <c r="W22" s="5"/>
+    </row>
+    <row r="23" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B23" s="31"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="5"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="41"/>
+      <c r="J23" s="41"/>
+      <c r="K23" s="41"/>
+      <c r="L23" s="41"/>
+      <c r="M23" s="41"/>
+      <c r="N23" s="41"/>
+      <c r="O23" s="41"/>
+      <c r="Q23" s="5"/>
+      <c r="S23" s="4"/>
+      <c r="T23" s="5"/>
+      <c r="U23" s="5"/>
+      <c r="W23" s="5"/>
+    </row>
+    <row r="24" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B24" s="31"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="5"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="41"/>
+      <c r="J24" s="41"/>
+      <c r="K24" s="41" t="s">
+        <v>86</v>
+      </c>
+      <c r="L24" s="42" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q24" s="5"/>
+      <c r="S24" s="4"/>
+      <c r="T24" s="5"/>
+      <c r="U24" s="5"/>
+      <c r="W24" s="5"/>
+    </row>
+    <row r="25" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B25" s="31"/>
+      <c r="D25" s="4"/>
+      <c r="F25" s="5"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="41"/>
+      <c r="J25" s="41"/>
+      <c r="K25" s="41"/>
+      <c r="L25" s="41" t="s">
+        <v>136</v>
+      </c>
+      <c r="M25" s="41" t="s">
+        <v>136</v>
+      </c>
+      <c r="N25" s="41" t="s">
+        <v>136</v>
+      </c>
+      <c r="O25" s="41" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q25" s="5"/>
+      <c r="T25" s="5"/>
+      <c r="U25" s="5"/>
+      <c r="W25" s="5"/>
+    </row>
+    <row r="26" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B26" s="31"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="5"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="41"/>
+      <c r="J26" s="41"/>
+      <c r="K26" s="41"/>
+      <c r="L26" s="41"/>
+      <c r="M26" s="41"/>
+      <c r="N26" s="41"/>
+      <c r="O26" s="41"/>
+      <c r="Q26" s="5"/>
+      <c r="S26" s="4"/>
+      <c r="T26" s="5"/>
+      <c r="U26" s="5"/>
+      <c r="W26" s="5"/>
+    </row>
+    <row r="27" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B27" s="31"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="5"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="41"/>
+      <c r="J27" s="41"/>
+      <c r="K27" s="41" t="s">
+        <v>86</v>
+      </c>
+      <c r="L27" s="42" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q27" s="5"/>
+      <c r="S27" s="4"/>
+      <c r="T27" s="5"/>
+      <c r="U27" s="5"/>
+      <c r="W27" s="5"/>
+    </row>
+    <row r="28" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B28" s="31"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="5"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="41"/>
+      <c r="J28" s="41"/>
+      <c r="K28" s="41"/>
+      <c r="L28" s="41" t="s">
+        <v>136</v>
+      </c>
+      <c r="M28" s="41" t="s">
+        <v>136</v>
+      </c>
+      <c r="N28" s="41" t="s">
+        <v>136</v>
+      </c>
+      <c r="O28" s="41" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q28" s="5"/>
+      <c r="S28" s="4"/>
+      <c r="T28" s="5"/>
+      <c r="U28" s="5"/>
+      <c r="W28" s="5"/>
+    </row>
+    <row r="29" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B29" s="31"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="5"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="41"/>
+      <c r="J29" s="41"/>
+      <c r="K29" s="41"/>
+      <c r="L29" s="41"/>
+      <c r="M29" s="41"/>
+      <c r="N29" s="41"/>
+      <c r="O29" s="41"/>
+      <c r="Q29" s="5"/>
+      <c r="S29" s="4"/>
+      <c r="T29" s="5"/>
+      <c r="U29" s="5"/>
+      <c r="W29" s="5"/>
+    </row>
+    <row r="30" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B30" s="31"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="5"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="41"/>
+      <c r="J30" s="41"/>
+      <c r="K30" s="41"/>
+      <c r="L30" s="41"/>
+      <c r="M30" s="41"/>
+      <c r="N30" s="41"/>
+      <c r="O30" s="41"/>
+      <c r="Q30" s="5"/>
+      <c r="S30" s="4"/>
+      <c r="T30" s="5"/>
+      <c r="U30" s="5"/>
+      <c r="W30" s="5"/>
+    </row>
+    <row r="31" spans="2:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B31" s="31"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="8"/>
+      <c r="H31" s="6"/>
+      <c r="I31" s="7"/>
+      <c r="J31" s="7"/>
+      <c r="K31" s="7"/>
+      <c r="L31" s="7"/>
+      <c r="M31" s="7"/>
+      <c r="N31" s="7"/>
+      <c r="O31" s="7"/>
+      <c r="P31" s="7"/>
+      <c r="Q31" s="8"/>
+      <c r="S31" s="6"/>
+      <c r="T31" s="8"/>
+      <c r="U31" s="5"/>
+      <c r="W31" s="5"/>
+    </row>
+    <row r="32" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B32" s="31"/>
+      <c r="D32" s="4"/>
+      <c r="U32" s="5"/>
+      <c r="W32" s="5"/>
+    </row>
+    <row r="33" spans="2:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B33" s="31"/>
+      <c r="D33" s="6"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+      <c r="G33" s="7"/>
+      <c r="H33" s="7"/>
+      <c r="I33" s="7"/>
+      <c r="J33" s="7"/>
+      <c r="K33" s="7"/>
+      <c r="L33" s="7"/>
+      <c r="M33" s="7"/>
+      <c r="N33" s="7"/>
+      <c r="O33" s="7"/>
+      <c r="P33" s="7"/>
+      <c r="Q33" s="7"/>
+      <c r="R33" s="7"/>
+      <c r="S33" s="7"/>
+      <c r="T33" s="7"/>
+      <c r="U33" s="8"/>
+      <c r="W33" s="5"/>
+    </row>
+    <row r="34" spans="2:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B34" s="31"/>
+      <c r="W34" s="5"/>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B35" s="31"/>
+      <c r="D35" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="2"/>
+      <c r="K35" s="2"/>
+      <c r="L35" s="2"/>
+      <c r="M35" s="2"/>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
+      <c r="P35" s="2"/>
+      <c r="Q35" s="2"/>
+      <c r="R35" s="2"/>
+      <c r="S35" s="2"/>
+      <c r="T35" s="2"/>
+      <c r="U35" s="3"/>
+      <c r="W35" s="5"/>
+    </row>
+    <row r="36" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B36" s="31"/>
+      <c r="D36" s="4"/>
+      <c r="U36" s="5"/>
+      <c r="W36" s="5"/>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B37" s="31"/>
+      <c r="D37" s="4"/>
+      <c r="U37" s="5"/>
+      <c r="W37" s="5"/>
+    </row>
+    <row r="38" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B38" s="31"/>
+      <c r="D38" s="4"/>
+      <c r="U38" s="5"/>
+      <c r="W38" s="5"/>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B39" s="31"/>
+      <c r="D39" s="4"/>
+      <c r="U39" s="5"/>
+      <c r="W39" s="5"/>
+    </row>
+    <row r="40" spans="2:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B40" s="31"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="7"/>
+      <c r="F40" s="7"/>
+      <c r="G40" s="7"/>
+      <c r="H40" s="7"/>
+      <c r="I40" s="7"/>
+      <c r="J40" s="7"/>
+      <c r="K40" s="7"/>
+      <c r="L40" s="7"/>
+      <c r="M40" s="7"/>
+      <c r="N40" s="7"/>
+      <c r="O40" s="7"/>
+      <c r="P40" s="7"/>
+      <c r="Q40" s="7"/>
+      <c r="R40" s="7"/>
+      <c r="S40" s="7"/>
+      <c r="T40" s="7"/>
+      <c r="U40" s="8"/>
+      <c r="W40" s="5"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B41" s="31"/>
+      <c r="W41" s="5"/>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B42" s="31"/>
+      <c r="W42" s="5"/>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B43" s="31"/>
+      <c r="W43" s="5"/>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B44" s="31"/>
+      <c r="W44" s="5"/>
+    </row>
+    <row r="45" spans="2:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B45" s="32"/>
+      <c r="C45" s="7"/>
+      <c r="D45" s="7"/>
+      <c r="E45" s="7"/>
+      <c r="F45" s="7"/>
+      <c r="G45" s="7"/>
+      <c r="H45" s="7"/>
+      <c r="I45" s="7"/>
+      <c r="J45" s="7"/>
+      <c r="K45" s="7"/>
+      <c r="L45" s="7"/>
+      <c r="M45" s="7"/>
+      <c r="N45" s="7"/>
+      <c r="O45" s="7"/>
+      <c r="P45" s="7"/>
+      <c r="Q45" s="7"/>
+      <c r="R45" s="7"/>
+      <c r="S45" s="7"/>
+      <c r="T45" s="7"/>
+      <c r="U45" s="7"/>
+      <c r="V45" s="7"/>
+      <c r="W45" s="8"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>